--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_164_R17.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_164_R17.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9782</v>
+        <v>6.9282</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8496</v>
+        <v>5.9676</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1286</v>
+        <v>0.9606</v>
       </c>
       <c r="G2" t="n">
         <v>2.9877</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0611</v>
+        <v>-0.1111</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1019</v>
+        <v>0.016</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0409</v>
+        <v>-0.1272</v>
       </c>
       <c r="V2" t="n">
         <v>2.428</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.202</v>
+        <v>4.8831</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5943</v>
+        <v>3.7123</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6077</v>
+        <v>1.1708</v>
       </c>
       <c r="G3" t="n">
         <v>3.7572</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2825</v>
+        <v>-0.0365</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0474</v>
+        <v>0.1654</v>
       </c>
       <c r="U3" t="n">
-        <v>0.235</v>
+        <v>-0.2018</v>
       </c>
       <c r="V3" t="n">
         <v>0.9304</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2235</v>
+        <v>2.4553</v>
       </c>
       <c r="E4" t="n">
-        <v>2.512</v>
+        <v>1.3425</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7115</v>
+        <v>1.1129</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8974</v>
+        <v>0.9671</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.1573</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8264</v>
+        <v>0.8098</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6807</v>
+        <v>1.2279</v>
       </c>
       <c r="K4" t="n">
-        <v>0.168</v>
+        <v>-0.0602</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5127</v>
+        <v>1.2882</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7833</v>
+        <v>-0.2608</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.097</v>
+        <v>0.2175</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6862</v>
+        <v>-0.4783</v>
       </c>
       <c r="P4" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0941</v>
+        <v>-0.0452</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9911</v>
+        <v>-0.0272</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1031</v>
+        <v>-0.018</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5226</v>
+        <v>2.2626</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3425</v>
+        <v>2.1896</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1801</v>
+        <v>0.073</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9671</v>
+        <v>0.8974</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1573</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8098</v>
+        <v>0.8264</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2279</v>
+        <v>2.6807</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0602</v>
+        <v>0.168</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2882</v>
+        <v>2.5127</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2608</v>
+        <v>-1.7833</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2175</v>
+        <v>-0.097</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4783</v>
+        <v>-1.6862</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.022</v>
+        <v>1.1332</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0272</v>
+        <v>0.6686</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0492</v>
+        <v>0.4646</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.722</v>
+        <v>1.2159</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8343</v>
+        <v>1.1266</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1123</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0.3782</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3258</v>
+        <v>0.8197</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4312</v>
+        <v>0.7235</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1054</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6778999999999999</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8866000000000001</v>
+        <v>0.0295</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0381</v>
+        <v>0.5084</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8485</v>
+        <v>-0.4788</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2907</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6655</v>
+        <v>0.2506</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2829</v>
+        <v>0.2636</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3826</v>
+        <v>-0.013</v>
       </c>
       <c r="V7" t="n">
         <v>0.1418</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1912</v>
+        <v>-1.1813</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6385</v>
+        <v>-0.6473</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5527</v>
+        <v>-0.534</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7241</v>
+        <v>-0.0137</v>
       </c>
       <c r="H8" t="n">
-        <v>3.049</v>
+        <v>0.5451</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3249</v>
+        <v>-0.5587</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4576</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1999</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2576</v>
+        <v>0.0736</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7334</v>
+        <v>-0.6755</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1509</v>
+        <v>-0.0431</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5825</v>
+        <v>-0.6323</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.7834</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4042</v>
+        <v>-0.2399</v>
       </c>
       <c r="T8" t="n">
-        <v>0.543</v>
+        <v>-0.1494</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1388</v>
+        <v>-0.0905</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3158</v>
+        <v>-1.2264</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6473</v>
+        <v>-0.9372</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6684</v>
+        <v>-0.2892</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0137</v>
+        <v>-0.7467</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5451</v>
+        <v>-0.2749</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5587</v>
+        <v>-0.4718</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6618000000000001</v>
+        <v>-0.4145</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5881999999999999</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0736</v>
+        <v>0.2676</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6755</v>
+        <v>-0.3322</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0431</v>
+        <v>0.4071</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6323</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3743</v>
+        <v>-0.9436</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1494</v>
+        <v>-0.5228</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2249</v>
+        <v>-0.4208</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4953</v>
+        <v>-1.239</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9372</v>
+        <v>-1.6926</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5580000000000001</v>
+        <v>0.4536</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7467</v>
+        <v>-1.8986</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2749</v>
+        <v>0.7816</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4718</v>
+        <v>-2.6802</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4145</v>
+        <v>-0.2187</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6820000000000001</v>
+        <v>1.2471</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2676</v>
+        <v>-1.4658</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3322</v>
+        <v>-1.6799</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4071</v>
+        <v>-0.4655</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-1.2144</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2125</v>
+        <v>0.6596</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5228</v>
+        <v>0.8456</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6897</v>
+        <v>-0.186</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3177</v>
+        <v>-1.4794</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4692</v>
+        <v>-0.725</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8485</v>
+        <v>-0.7544</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7148</v>
+        <v>1.7241</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0155</v>
+        <v>3.049</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6993</v>
+        <v>-1.3249</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0536</v>
+        <v>3.4576</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0168</v>
+        <v>3.1999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0368</v>
+        <v>0.2576</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7684</v>
+        <v>-1.7334</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0323</v>
+        <v>-0.1509</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7361</v>
+        <v>-1.5825</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9278</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R11" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3971</v>
+        <v>0.116</v>
       </c>
       <c r="T11" t="n">
-        <v>0.637</v>
+        <v>0.4564</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2399</v>
+        <v>-0.3404</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6002</v>
+        <v>-2.4789</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5497</v>
+        <v>-0.6304</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0505</v>
+        <v>-1.8485</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8986</v>
+        <v>-0.7148</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7816</v>
+        <v>-0.0155</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.6802</v>
+        <v>-0.6993</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2187</v>
+        <v>0.0536</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2471</v>
+        <v>0.0168</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4658</v>
+        <v>0.0368</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6799</v>
+        <v>-0.7684</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4655</v>
+        <v>-0.0323</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2144</v>
+        <v>-0.7361</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7016</v>
+        <v>0.2359</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0114</v>
+        <v>0.4758</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6901</v>
+        <v>-0.2399</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.967</v>
+        <v>-3.5481</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9288</v>
+        <v>-2.5436</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0382</v>
+        <v>-1.0046</v>
       </c>
       <c r="G13" t="n">
         <v>-4.2214</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0224</v>
+        <v>0.4413</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2794</v>
+        <v>0.6647</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.257</v>
+        <v>-0.2234</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.874499999999996</v>
+        <v>6.621499999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>6.923899999999999</v>
+        <v>7.6709</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.049199999999999</v>
+        <v>-1.0492</v>
       </c>
       <c r="G14" t="n">
         <v>1.825799999999998</v>
       </c>
       <c r="H14" t="n">
-        <v>8.919499999999998</v>
+        <v>8.919499999999999</v>
       </c>
       <c r="I14" t="n">
         <v>-7.093500000000001</v>
@@ -1546,10 +1546,10 @@
         <v>13.9172</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5331</v>
+        <v>2.28</v>
       </c>
       <c r="T14" t="n">
-        <v>2.833499999999999</v>
+        <v>3.5802</v>
       </c>
       <c r="U14" t="n">
         <v>-1.3002</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.97</v>
+        <v>5.8464</v>
       </c>
       <c r="E15" t="n">
-        <v>5.8588</v>
+        <v>5.387</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1112</v>
+        <v>0.4593</v>
       </c>
       <c r="G15" t="n">
         <v>7.28</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1349</v>
+        <v>-0.2585</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9085</v>
+        <v>0.4367</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0433</v>
+        <v>-0.6952</v>
       </c>
       <c r="V15" t="n">
         <v>1.6083</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.575</v>
+        <v>4.6036</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5468</v>
+        <v>4.4289</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0282</v>
+        <v>0.1747</v>
       </c>
       <c r="G16" t="n">
         <v>3.6178</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4345</v>
+        <v>-0.4059</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1889</v>
+        <v>0.0709</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6234</v>
+        <v>-0.4769</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1094</v>
+        <v>3.0967</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2575</v>
+        <v>2.4934</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1481</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>1.9596</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4739</v>
+        <v>-0.4865</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1221</v>
+        <v>0.358</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.596</v>
+        <v>-0.8445</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2544</v>
+        <v>0.4173</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4866</v>
+        <v>1.4251</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2322</v>
+        <v>-1.0077</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6183999999999999</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0868</v>
+        <v>0.2497</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0895</v>
+        <v>0.0279</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0026</v>
+        <v>0.2219</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1418</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7109</v>
+        <v>0.2435</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2239</v>
+        <v>0.6957</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9348</v>
+        <v>-0.4523</v>
       </c>
       <c r="G19" t="n">
         <v>0.3319</v>
@@ -1936,13 +1936,13 @@
         <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5942</v>
+        <v>-0.6398</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5228</v>
+        <v>-0.051</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0714</v>
+        <v>-0.5889</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.381</v>
+        <v>-0.5496</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9123</v>
+        <v>1.6201</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2934</v>
+        <v>-2.1697</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2864</v>
@@ -2014,13 +2014,13 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7183</v>
+        <v>0.1131</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0455</v>
+        <v>-0.3378</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3273</v>
+        <v>0.4509</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. STEVENS</t>
+          <t>A. M'BAYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3976</v>
+        <v>-1.7195</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8678</v>
+        <v>0.8035</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5298</v>
+        <v>-2.523</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.8029</v>
+        <v>-0.777</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.8069</v>
+        <v>-1.4262</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0039</v>
+        <v>0.6492</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6301</v>
+        <v>2.0573</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.0592</v>
+        <v>-0.1744</v>
       </c>
       <c r="L21" t="n">
-        <v>2.4291</v>
+        <v>2.2317</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1729</v>
+        <v>-2.8343</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7477</v>
+        <v>-1.2518</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4252</v>
+        <v>-1.5825</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8719</v>
+        <v>0.1092</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0148</v>
+        <v>-0.094</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8571</v>
+        <v>0.2032</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3943</v>
+        <v>-0.8197</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.2525</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. M'BAYE</t>
+          <t>L. STEVENS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9212</v>
+        <v>-2.4192</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1401</v>
+        <v>-1.8114</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7811</v>
+        <v>-0.6078</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.777</v>
+        <v>-3.8029</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4262</v>
+        <v>-4.8069</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6492</v>
+        <v>1.0039</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0573</v>
+        <v>-1.6301</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1744</v>
+        <v>-4.0592</v>
       </c>
       <c r="L22" t="n">
-        <v>2.2317</v>
+        <v>2.4291</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.8343</v>
+        <v>-2.1729</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2518</v>
+        <v>-0.7477</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5825</v>
+        <v>-1.4252</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0925</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0376</v>
+        <v>0.0712</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0549</v>
+        <v>0.7791</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8197</v>
+        <v>-0.3943</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.2525</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8197</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.503</v>
+        <v>-4.8042</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7203</v>
+        <v>-5.6639</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2173</v>
+        <v>0.8597</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9252</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>2.2958</v>
+        <v>0.9946</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9189</v>
+        <v>0.9752</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3769</v>
+        <v>0.0193</v>
       </c>
       <c r="V23" t="n">
         <v>0.1418</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.8697</v>
+        <v>-8.230499999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.5085</v>
+        <v>-8.329000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3612</v>
+        <v>0.0985</v>
       </c>
       <c r="G24" t="n">
         <v>-6.6051</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3394</v>
+        <v>0.2998</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3364</v>
+        <v>-0.1568</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0031</v>
+        <v>0.4567</v>
       </c>
       <c r="V24" t="n">
         <v>0.3943</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.8746</v>
+        <v>-3.515500000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>1.049199999999999</v>
+        <v>1.049399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.923900000000001</v>
+        <v>-4.565000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-1.825699999999999</v>
@@ -2404,13 +2404,13 @@
         <v>12.7575</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5332</v>
+        <v>0.8259999999999998</v>
       </c>
       <c r="T25" t="n">
-        <v>1.3004</v>
+        <v>1.3003</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.8334</v>
+        <v>-0.4743999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-1.3558</v>
